--- a/data/memories/memory_01/locales/es/documents/reception/Suppliers.xlsx
+++ b/data/memories/memory_01/locales/es/documents/reception/Suppliers.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Suppliers</t>
+          <t>Proveedores</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,62 +469,62 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reception</t>
+          <t>Recepción</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Regular Suppliers</t>
+          <t>Proveedores habituales</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>Proveedor</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Servicio</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vending Solutions S.L.</t>
+          <t>Soluciones Vending S.L.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vending</t>
+          <t>Venta</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Printer Maintenance</t>
+          <t>Mantenimiento de la impresora</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Printers</t>
+          <t>Impresoras</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cleaning Company</t>
+          <t>Empresa de limpieza</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Limpieza</t>
         </is>
       </c>
     </row>
